--- a/data/export/2026-10-20-182路.xlsx
+++ b/data/export/2026-10-20-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC9"/>
+  <dimension ref="A1:AC17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -441,7 +441,7 @@
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
@@ -632,32 +632,36 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -665,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -689,33 +693,37 @@
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>1/13</t>
         </is>
       </c>
     </row>
@@ -743,32 +751,36 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:25</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -776,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -800,17 +812,17 @@
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
@@ -820,13 +832,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -854,32 +870,36 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:39</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -887,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -911,33 +931,37 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" s="2" t="inlineStr"/>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -998,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1037,7 +1061,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1048,7 +1072,7 @@
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1076,32 +1100,36 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:58</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1109,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1133,17 +1161,17 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
@@ -1153,13 +1181,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1252,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1270,7 +1302,7 @@
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1363,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1381,7 +1413,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1389,22 +1421,22 @@
       <c r="A9" s="2" t="inlineStr"/>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>沪A35717D</t>
+          <t>沪A08953A</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>07:15</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1437,12 +1469,12 @@
       <c r="M9" s="2" t="inlineStr"/>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>06:02</t>
+          <t>06:32</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1456,7 +1488,7 @@
       <c r="T9" s="2" t="inlineStr"/>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
@@ -1492,7 +1524,903 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr"/>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>07:22</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr"/>
+      <c r="R10" s="2" t="inlineStr"/>
+      <c r="S10" s="2" t="inlineStr"/>
+      <c r="T10" s="2" t="inlineStr"/>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>—/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>07:22</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr"/>
+      <c r="S11" s="2" t="inlineStr"/>
+      <c r="T11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>—/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>07:22</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr"/>
+      <c r="T12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>—/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>07:22</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr"/>
+      <c r="S13" s="2" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>1/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>07:36</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>07:02</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>07:22</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="inlineStr"/>
+      <c r="T14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>07:36</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>—/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>沪A12050A</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>07:48</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>07:22</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>07:22</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr"/>
+      <c r="S15" s="2" t="inlineStr"/>
+      <c r="T15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>07:48</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>—/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>沪A67983D</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>07:22</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr"/>
+      <c r="S16" s="2" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr"/>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>3/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr"/>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>07:22</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="R17" s="2" t="inlineStr"/>
+      <c r="S17" s="2" t="inlineStr"/>
+      <c r="T17" s="2" t="inlineStr"/>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>—/13</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-20-182路.xlsx
+++ b/data/export/2026-10-20-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC17"/>
+  <dimension ref="A1:AC25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>1/13</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,14 +827,14 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
           <t>75.0</t>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -880,12 +880,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>07:39</t>
+          <t>07:40</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -956,12 +956,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -989,32 +989,36 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1022,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1046,17 +1050,17 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
@@ -1066,13 +1070,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1176,14 +1184,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
           <t>83.0</t>
@@ -1191,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1219,32 +1227,36 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
           <t>06:12</t>
@@ -1252,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1276,33 +1288,37 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1330,32 +1346,36 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1363,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1387,33 +1407,37 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1441,32 +1465,36 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
           <t>06:32</t>
@@ -1474,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1498,33 +1526,37 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" s="2" t="inlineStr"/>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1585,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1624,7 +1656,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1635,7 +1667,7 @@
       <c r="AB10" s="2" t="inlineStr"/>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -1663,32 +1695,36 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>102分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1696,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1720,33 +1756,37 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>102.0</t>
+        </is>
+      </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1807,7 +1847,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1857,7 +1897,7 @@
       <c r="AB12" s="2" t="inlineStr"/>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -1918,7 +1958,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1972,7 +2012,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>1/13</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -2033,7 +2073,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2083,7 +2123,7 @@
       <c r="AB14" s="2" t="inlineStr"/>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -2144,7 +2184,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2194,7 +2234,7 @@
       <c r="AB15" s="2" t="inlineStr"/>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -2255,7 +2295,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2304,12 +2344,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -2317,22 +2357,22 @@
       <c r="A17" s="2" t="inlineStr"/>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>沪A67026D</t>
+          <t>沪A68397D</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>08:15</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2370,7 +2410,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2384,43 +2424,959 @@
       <c r="T17" s="2" t="inlineStr"/>
       <c r="U17" s="2" t="inlineStr">
         <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
           <t>08:15</t>
         </is>
       </c>
-      <c r="V17" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>08:22</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr"/>
+      <c r="S18" s="2" t="inlineStr"/>
+      <c r="T18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W17" s="2" t="inlineStr">
+      <c r="W18" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X17" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y17" s="2" t="inlineStr">
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z17" s="2" t="inlineStr">
+      <c r="Z18" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr"/>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>08:22</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr"/>
+      <c r="R19" s="2" t="inlineStr"/>
+      <c r="S19" s="2" t="inlineStr"/>
+      <c r="T19" s="2" t="inlineStr"/>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>沪A02126A</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>07:52</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>08:22</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="R20" s="2" t="inlineStr"/>
+      <c r="S20" s="2" t="inlineStr"/>
+      <c r="T20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB17" s="2" t="inlineStr"/>
-      <c r="AC17" s="2" t="inlineStr">
-        <is>
-          <t>—/13</t>
+      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>06:12</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>08:22</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr"/>
+      <c r="R21" s="2" t="inlineStr"/>
+      <c r="S21" s="2" t="inlineStr"/>
+      <c r="T21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr"/>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>08:22</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>5/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>沪A08953A</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>06:32</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>08:22</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr"/>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>7/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr"/>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>08:22</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr"/>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>102.0</t>
+        </is>
+      </c>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>9/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>08:22</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr"/>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr"/>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-20-182路.xlsx
+++ b/data/export/2026-10-20-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC25"/>
+  <dimension ref="A1:AC29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1584,32 +1584,36 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
           <t>06:42</t>
@@ -1617,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1641,17 +1645,17 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
@@ -1661,13 +1665,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB10" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1705,24 +1713,24 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>102分钟</t>
+          <t>108分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1732,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1781,12 +1789,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>108.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1814,32 +1822,36 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1847,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1871,33 +1883,37 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1925,32 +1941,36 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1958,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1982,37 +2002,37 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -2040,32 +2060,36 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
           <t>07:02</t>
@@ -2073,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2097,33 +2121,37 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -2184,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2295,7 +2323,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2334,7 +2362,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2349,7 +2377,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -2410,7 +2438,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2464,7 +2492,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -2525,7 +2553,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2640,7 +2668,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2755,7 +2783,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2866,7 +2894,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2920,7 +2948,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -2981,7 +3009,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3096,7 +3124,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3150,7 +3178,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -3211,7 +3239,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3260,12 +3288,12 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>108.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -3326,7 +3354,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3370,13 +3398,477 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB25" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>10/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>09:02</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr"/>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>9/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr"/>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>09:02</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr"/>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>80.5</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr"/>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>07:02</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>09:02</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr"/>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>7/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr"/>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>沪A67983D</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>09:02</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr"/>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-20-182路.xlsx
+++ b/data/export/2026-10-20-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC29"/>
+  <dimension ref="A1:AC31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,17 +832,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,22 +1065,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2179,32 +2179,36 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
           <t>07:22</t>
@@ -2212,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2236,33 +2240,37 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -2290,32 +2298,36 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2323,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2347,17 +2359,17 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
@@ -2367,17 +2379,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -2405,32 +2417,36 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>101分钟</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2438,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2462,17 +2478,17 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
@@ -2482,17 +2498,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2520,32 +2536,36 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2553,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2577,37 +2597,37 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2668,7 +2688,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2722,7 +2742,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2914,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3009,7 +3029,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3063,7 +3083,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -3124,7 +3144,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3178,7 +3198,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -3239,7 +3259,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3293,7 +3313,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -3354,7 +3374,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3469,7 +3489,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3584,7 +3604,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3638,7 +3658,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -3699,7 +3719,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3753,7 +3773,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -3761,22 +3781,22 @@
       <c r="A29" s="2" t="inlineStr"/>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>沪A67983D</t>
+          <t>沪A12050A</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
           <t>川沙客运站</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>09:50</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -3809,12 +3829,12 @@
       <c r="M29" s="2" t="inlineStr"/>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>06:02</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3853,22 +3873,252 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>12/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr"/>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>沪A67983D</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB29" s="2" t="inlineStr">
-        <is>
-          <t>80.0</t>
-        </is>
-      </c>
-      <c r="AC29" s="2" t="inlineStr">
-        <is>
-          <t>2/14</t>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr"/>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr"/>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>89.5</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>8/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-20-182路.xlsx
+++ b/data/export/2026-10-20-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC31"/>
+  <dimension ref="A1:AC39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,12 +713,12 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,22 +827,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1184,22 +1184,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,22 +1303,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1546,17 +1546,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1660,22 +1660,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1779,17 +1779,17 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>108.0</t>
+          <t>93.5</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2022,12 +2022,12 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2427,12 +2427,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>101分钟</t>
+          <t>100分钟</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2493,22 +2493,22 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -2546,24 +2546,24 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>93分钟</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2622,12 +2622,12 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -2655,32 +2655,36 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2688,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2712,37 +2716,37 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2803,7 +2807,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2842,7 +2846,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2881,32 +2885,36 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
           <t>06:12</t>
@@ -2914,7 +2922,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2938,37 +2946,37 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -3029,7 +3037,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3068,7 +3076,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
@@ -3111,32 +3119,36 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
           <t>06:32</t>
@@ -3144,7 +3156,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3168,17 +3180,17 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
@@ -3188,17 +3200,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -3226,32 +3238,36 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -3259,7 +3275,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3283,32 +3299,32 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA24" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>108.0</t>
+          <t>93.5</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3341,32 +3357,36 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
           <t>06:42</t>
@@ -3374,7 +3394,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3398,37 +3418,37 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -3489,7 +3509,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3543,7 +3563,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -3571,32 +3591,36 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -3604,7 +3628,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3628,17 +3652,17 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
@@ -3648,12 +3672,12 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
@@ -3719,7 +3743,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3758,7 +3782,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3773,7 +3797,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -3834,7 +3858,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3949,7 +3973,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4011,22 +4035,22 @@
       <c r="A31" s="2" t="inlineStr"/>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>沪A67026D</t>
+          <t>沪A68397D</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
           <t>川沙客运站</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>10:15</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -4064,7 +4088,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4078,45 +4102,961 @@
       <c r="T31" s="2" t="inlineStr"/>
       <c r="U31" s="2" t="inlineStr">
         <is>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>87.5</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>9/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr"/>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
           <t>10:15</t>
         </is>
       </c>
-      <c r="V31" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W31" s="2" t="inlineStr">
+      <c r="W32" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X31" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y31" s="2" t="inlineStr">
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z31" s="2" t="inlineStr">
+      <c r="Z32" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
+      <c r="AA32" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB31" s="2" t="inlineStr">
-        <is>
-          <t>89.5</t>
-        </is>
-      </c>
-      <c r="AC31" s="2" t="inlineStr">
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>10/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr"/>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr"/>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr"/>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>沪A02126A</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>07:52</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr"/>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr"/>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>06:12</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr"/>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr"/>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr"/>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr"/>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>93.5</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>13/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr"/>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>84.5</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>5/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr"/>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>07:02</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr"/>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
         <is>
           <t>8/14</t>
         </is>

--- a/data/export/2026-10-20-182路.xlsx
+++ b/data/export/2026-10-20-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC39"/>
+  <dimension ref="A1:AC45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,17 +708,17 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,17 +832,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>85.3</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,22 +946,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,22 +1065,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1189,17 +1189,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,22 +1303,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1903,17 +1903,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2017,17 +2017,17 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2141,17 +2141,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2255,22 +2255,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2374,22 +2374,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2498,17 +2498,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>85.3</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2612,22 +2612,22 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2807,7 +2807,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2922,7 +2922,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2961,22 +2961,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -3037,7 +3037,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -3210,7 +3210,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -3275,7 +3275,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3394,7 +3394,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3448,7 +3448,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -3476,32 +3476,36 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -3509,7 +3513,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3533,17 +3537,17 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
@@ -3553,17 +3557,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -3601,12 +3605,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>70分钟</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
@@ -3628,7 +3632,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3667,17 +3671,17 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA27" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
@@ -3710,32 +3714,36 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
           <t>07:02</t>
@@ -3743,7 +3751,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3767,17 +3775,17 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
@@ -3787,17 +3795,17 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -3825,32 +3833,36 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>66分钟</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
           <t>07:22</t>
@@ -3858,7 +3870,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3882,37 +3894,37 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -3940,32 +3952,36 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -3973,7 +3989,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3997,37 +4013,37 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -4055,32 +4071,36 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -4088,7 +4108,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4112,17 +4132,17 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
@@ -4132,17 +4152,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>85.3</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -4170,32 +4190,36 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -4203,7 +4227,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4227,37 +4251,37 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -4285,32 +4309,36 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -4318,7 +4346,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4342,17 +4370,17 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
@@ -4362,17 +4390,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4461,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4472,7 +4500,7 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
@@ -4511,32 +4539,36 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
           <t>06:12</t>
@@ -4544,7 +4576,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4568,37 +4600,37 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -4659,7 +4691,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4713,7 +4745,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -4774,7 +4806,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4889,7 +4921,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4943,7 +4975,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -4951,22 +4983,22 @@
       <c r="A39" s="2" t="inlineStr"/>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>沪A32298D</t>
+          <t>沪A55712D</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
           <t>川沙客运站</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -4999,12 +5031,12 @@
       <c r="M39" s="2" t="inlineStr"/>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>07:02</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5018,47 +5050,733 @@
       <c r="T39" s="2" t="inlineStr"/>
       <c r="U39" s="2" t="inlineStr">
         <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>77.3</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr"/>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
           <t>11:30</t>
         </is>
       </c>
-      <c r="V39" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>07:02</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W39" s="2" t="inlineStr">
+      <c r="W40" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X39" s="2" t="inlineStr">
+      <c r="X40" s="2" t="inlineStr">
         <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Y39" s="2" t="inlineStr">
+      <c r="Y40" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z39" s="2" t="inlineStr">
+      <c r="Z40" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA39" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB39" s="2" t="inlineStr">
-        <is>
-          <t>87.0</t>
-        </is>
-      </c>
-      <c r="AC39" s="2" t="inlineStr">
-        <is>
-          <t>8/14</t>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>77.5</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr"/>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>沪A67983D</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr"/>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>80.3</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr"/>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>沪A12050A</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>07:22</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr"/>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr"/>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>9/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr"/>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>沪A02126A</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>07:52</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr"/>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr"/>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr"/>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr"/>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>06:12</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr"/>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>5/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-20-182路.xlsx
+++ b/data/export/2026-10-20-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC45"/>
+  <dimension ref="A1:AC51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,22 +827,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>85.3</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1184,14 +1184,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
           <t>83.7</t>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1427,17 +1427,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1660,22 +1660,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1784,17 +1784,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>93.5</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1898,14 +1898,14 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
           <t>83.5</t>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2022,17 +2022,17 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2136,17 +2136,17 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>74.7</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2255,7 +2255,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2389,7 +2389,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2493,22 +2493,22 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>85.3</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2622,7 +2622,7 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -2692,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2731,14 +2731,14 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
           <t>83.7</t>
@@ -2746,7 +2746,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -2807,7 +2807,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2851,13 +2851,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB20" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -2922,7 +2926,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2971,12 +2975,12 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -3037,7 +3041,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3081,17 +3085,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -3210,7 +3214,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3275,7 +3279,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3319,17 +3323,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>93.5</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3398,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3433,22 +3437,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -3513,7 +3517,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3552,14 +3556,14 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
           <t>83.5</t>
@@ -3567,7 +3571,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3632,7 +3636,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3676,17 +3680,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3755,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3790,17 +3794,17 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA28" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>74.7</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
@@ -3870,7 +3874,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3909,7 +3913,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -3924,7 +3928,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -3989,7 +3993,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4043,7 +4047,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -4081,12 +4085,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
@@ -4108,7 +4112,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4147,22 +4151,22 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>85.3</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -4200,19 +4204,19 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>76分钟</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
@@ -4227,7 +4231,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4276,7 +4280,7 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4346,7 +4350,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4385,14 +4389,14 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA33" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
           <t>83.7</t>
@@ -4400,7 +4404,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -4428,32 +4432,36 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
           <t>07:52</t>
@@ -4461,7 +4469,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4485,17 +4493,17 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
@@ -4505,13 +4513,17 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB34" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -4549,24 +4561,24 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>71分钟</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4576,7 +4588,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4625,12 +4637,12 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -4658,32 +4670,36 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -4691,7 +4707,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4715,17 +4731,17 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
@@ -4735,17 +4751,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -4773,32 +4789,36 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -4806,7 +4826,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4830,17 +4850,17 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
@@ -4850,17 +4870,17 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>93.5</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -4888,32 +4908,36 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
           <t>06:42</t>
@@ -4921,7 +4945,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4945,37 +4969,37 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA38" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -5003,32 +5027,36 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -5036,7 +5064,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5060,17 +5088,17 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
@@ -5080,17 +5108,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -5118,32 +5146,36 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
           <t>07:02</t>
@@ -5151,7 +5183,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5175,32 +5207,32 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA40" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>74.7</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
@@ -5266,7 +5298,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5320,7 +5352,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -5381,7 +5413,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5420,7 +5452,7 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
@@ -5435,7 +5467,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5528,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5545,7 +5577,7 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
@@ -5611,7 +5643,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5655,13 +5687,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB44" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -5722,7 +5758,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5771,12 +5807,702 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr"/>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
           <t>81.0</t>
         </is>
       </c>
-      <c r="AC45" s="2" t="inlineStr">
+      <c r="AC46" s="2" t="inlineStr">
+        <is>
+          <t>7/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr"/>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr"/>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr"/>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>83.5</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr">
+        <is>
+          <t>10/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr"/>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>07:02</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr"/>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>74.7</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr"/>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>沪A68397D</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr"/>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>85.7</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr">
+        <is>
+          <t>13/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr"/>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>沪A12050A</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>07:22</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr"/>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr">
         <is>
           <t>5/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr"/>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr"/>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr"/>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>83.7</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>12/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-20-182路.xlsx
+++ b/data/export/2026-10-20-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC51"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1070,17 +1070,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1308,17 +1308,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1898,22 +1898,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2260,17 +2260,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2379,17 +2379,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2617,17 +2617,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2807,7 +2807,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
@@ -2926,7 +2926,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2970,17 +2970,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -3041,7 +3041,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3080,7 +3080,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -3214,7 +3214,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3452,7 +3452,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3556,22 +3556,22 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -3755,7 +3755,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -3993,7 +3993,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4037,17 +4037,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -4112,7 +4112,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4275,17 +4275,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -4350,7 +4350,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4469,7 +4469,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4508,12 +4508,12 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
@@ -4588,7 +4588,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4632,17 +4632,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -4707,7 +4707,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4746,7 +4746,7 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4865,7 +4865,7 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -4945,7 +4945,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4999,7 +4999,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -5183,7 +5183,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5265,32 +5265,36 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -5298,7 +5302,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5322,17 +5326,17 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
@@ -5342,17 +5346,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -5380,32 +5384,36 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
           <t>07:22</t>
@@ -5413,7 +5421,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5437,17 +5445,17 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
@@ -5457,17 +5465,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -5495,32 +5503,36 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -5528,7 +5540,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5552,17 +5564,17 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
@@ -5572,17 +5584,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -5610,32 +5622,36 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
           <t>07:52</t>
@@ -5643,7 +5659,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5667,27 +5683,27 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
@@ -5725,32 +5741,36 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
           <t>06:12</t>
@@ -5758,7 +5778,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5782,17 +5802,17 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
@@ -5802,17 +5822,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -5873,7 +5893,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5927,7 +5947,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -5955,32 +5975,36 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -5988,7 +6012,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6012,37 +6036,37 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y47" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA47" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -6103,7 +6127,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6218,7 +6242,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6333,7 +6357,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6377,17 +6401,17 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -6448,7 +6472,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6506,6 +6530,466 @@
         </is>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr"/>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>沪A02126A</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>07:52</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr"/>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr"/>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr"/>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr"/>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>78.5</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr"/>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr"/>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>78.3</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>5/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr"/>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr"/>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr"/>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>87.3</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>14/14</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-20-182路.xlsx
+++ b/data/export/2026-10-20-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC55"/>
+  <dimension ref="A1:AC58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,22 +827,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>85.7</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1665,17 +1665,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2493,22 +2493,22 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>85.7</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -2627,7 +2627,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2731,7 +2731,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -2807,7 +2807,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2926,7 +2926,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2980,7 +2980,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3041,7 +3041,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -3214,7 +3214,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3442,17 +3442,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3755,7 +3755,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -4112,7 +4112,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4151,22 +4151,22 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>85.7</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -4285,7 +4285,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -4350,7 +4350,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4389,7 +4389,7 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
@@ -4404,7 +4404,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -4469,7 +4469,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4588,7 +4588,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4642,7 +4642,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -4707,7 +4707,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4945,7 +4945,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4989,17 +4989,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -5064,7 +5064,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -5183,7 +5183,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5594,7 +5594,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -5659,7 +5659,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5763,12 +5763,12 @@
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5778,7 +5778,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5832,7 +5832,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -5860,32 +5860,36 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
           <t>06:42</t>
@@ -5893,7 +5897,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5917,17 +5921,17 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">
@@ -5937,17 +5941,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -5985,24 +5989,24 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>68分钟</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -6012,7 +6016,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6061,12 +6065,12 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -6127,7 +6131,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6209,32 +6213,36 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -6242,7 +6250,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6266,37 +6274,37 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA49" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>85.7</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -6472,7 +6480,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6511,7 +6519,7 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
@@ -6526,7 +6534,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -6587,7 +6595,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6702,7 +6710,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6756,7 +6764,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -6817,7 +6825,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6866,12 +6874,12 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -6932,7 +6940,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6990,6 +6998,351 @@
         </is>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr"/>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr"/>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>75.5</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr"/>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>沪A68397D</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr"/>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr"/>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>81.8</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>11/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr"/>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr"/>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr"/>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>83.7</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>13/14</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-20-182路.xlsx
+++ b/data/export/2026-10-20-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC58"/>
+  <dimension ref="A1:AC61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -837,12 +837,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1189,17 +1189,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1541,14 +1541,14 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
           <t>83.5</t>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2141,12 +2141,12 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>74.7</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -2627,7 +2627,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -2807,7 +2807,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2851,12 +2851,12 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2980,7 +2980,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -3041,7 +3041,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3080,7 +3080,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
@@ -3160,7 +3160,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3199,14 +3199,14 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
           <t>83.5</t>
@@ -3214,7 +3214,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3517,7 +3517,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3755,7 +3755,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3799,12 +3799,12 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>74.7</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4032,7 +4032,7 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
@@ -4112,7 +4112,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4161,12 +4161,12 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -4285,7 +4285,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -4350,7 +4350,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4394,17 +4394,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -4469,7 +4469,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4642,7 +4642,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -4707,7 +4707,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4746,7 +4746,7 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -5064,7 +5064,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5183,7 +5183,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5227,12 +5227,12 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>74.7</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
@@ -5302,7 +5302,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5341,7 +5341,7 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
@@ -5594,7 +5594,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -5659,7 +5659,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5703,12 +5703,12 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5832,7 +5832,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -6016,7 +6016,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6098,32 +6098,36 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M48" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
           <t>07:02</t>
@@ -6131,7 +6135,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6155,17 +6159,17 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z48" s="2" t="inlineStr">
@@ -6175,12 +6179,12 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>74.7</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
@@ -6223,24 +6227,24 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>70分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -6250,7 +6254,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6299,12 +6303,12 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -6447,32 +6451,36 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -6480,7 +6488,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6504,17 +6512,17 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y51" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z51" s="2" t="inlineStr">
@@ -6524,17 +6532,17 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -6562,32 +6570,36 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
           <t>07:52</t>
@@ -6595,7 +6607,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6619,17 +6631,17 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y52" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z52" s="2" t="inlineStr">
@@ -6639,12 +6651,12 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6710,7 +6722,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6749,7 +6761,7 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA53" s="2" t="inlineStr">
@@ -6825,7 +6837,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6940,7 +6952,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7055,7 +7067,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7170,7 +7182,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7219,12 +7231,12 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -7232,22 +7244,22 @@
       <c r="A58" s="2" t="inlineStr"/>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>沪A68870D</t>
+          <t>沪A08953A</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="E58" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -7280,12 +7292,12 @@
       <c r="M58" s="2" t="inlineStr"/>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>06:02</t>
+          <t>06:32</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7324,22 +7336,367 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>83.5</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>13/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr"/>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr"/>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr"/>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA58" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AB58" s="2" t="inlineStr">
-        <is>
-          <t>83.7</t>
-        </is>
-      </c>
-      <c r="AC58" s="2" t="inlineStr">
-        <is>
-          <t>13/14</t>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>80.5</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>9/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr"/>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>沪A67983D</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr"/>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr"/>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>79.5</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>7/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr"/>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr"/>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr"/>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>78.5</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>5/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-20-182路.xlsx
+++ b/data/export/2026-10-20-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC61"/>
+  <dimension ref="A1:AC67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,17 +832,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,14 +1065,14 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
           <t>80.8</t>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,14 +1303,14 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
           <t>81.0</t>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1427,17 +1427,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1779,22 +1779,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1903,17 +1903,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2498,17 +2498,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2612,14 +2612,14 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
           <t>80.8</t>
@@ -2627,7 +2627,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2741,7 +2741,7 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
@@ -2807,7 +2807,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2856,7 +2856,7 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>68.3</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2926,7 +2926,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2965,14 +2965,14 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
           <t>81.0</t>
@@ -2980,7 +2980,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -3041,7 +3041,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3085,17 +3085,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3199,7 +3199,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
@@ -3214,7 +3214,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3318,22 +3318,22 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA24" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -3398,7 +3398,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3437,7 +3437,7 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
@@ -3517,7 +3517,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3561,17 +3561,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4112,7 +4112,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4156,17 +4156,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -4231,7 +4231,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4270,14 +4270,14 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
           <t>80.8</t>
@@ -4285,7 +4285,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -4350,7 +4350,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4399,7 +4399,7 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -4469,7 +4469,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4518,7 +4518,7 @@
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>68.3</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4588,7 +4588,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4627,14 +4627,14 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
           <t>81.0</t>
@@ -4642,7 +4642,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -4707,7 +4707,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4751,17 +4751,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4865,22 +4865,22 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA37" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -4945,7 +4945,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4984,7 +4984,7 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
@@ -5064,7 +5064,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -5302,7 +5302,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5540,7 +5540,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5579,14 +5579,14 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA43" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
           <t>80.8</t>
@@ -5594,7 +5594,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -5659,7 +5659,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5708,7 +5708,7 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>68.3</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5778,7 +5778,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5817,14 +5817,14 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA45" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
           <t>81.0</t>
@@ -5832,7 +5832,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -5897,7 +5897,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5936,7 +5936,7 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
@@ -6016,7 +6016,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6060,17 +6060,17 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -6254,7 +6254,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6298,17 +6298,17 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -6461,12 +6461,12 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>71分钟</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
@@ -6488,7 +6488,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6537,7 +6537,7 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
@@ -6580,24 +6580,24 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>71分钟</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6607,7 +6607,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6656,7 +6656,7 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>68.3</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6689,32 +6689,36 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -6722,7 +6726,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6746,17 +6750,17 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z53" s="2" t="inlineStr">
@@ -6766,17 +6770,17 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -6804,32 +6808,36 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M54" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -6837,7 +6845,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6861,17 +6869,17 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z54" s="2" t="inlineStr">
@@ -6881,17 +6889,17 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -6919,32 +6927,36 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M55" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -6952,7 +6964,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6976,37 +6988,37 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA55" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -7067,7 +7079,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7106,7 +7118,7 @@
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
@@ -7149,32 +7161,36 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M57" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -7182,7 +7198,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7206,17 +7222,17 @@
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z57" s="2" t="inlineStr">
@@ -7226,17 +7242,17 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -7297,7 +7313,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7336,7 +7352,7 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
@@ -7351,7 +7367,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7428,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7461,7 +7477,7 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
@@ -7527,7 +7543,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7642,7 +7658,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7686,17 +7702,707 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>77.3</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr"/>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr"/>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>06:12</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr"/>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>12/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr"/>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr"/>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr"/>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>83.2</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>13/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr"/>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr"/>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr"/>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>80.8</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>9/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr"/>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr"/>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr"/>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>75.5</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr"/>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr"/>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr"/>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>79.5</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>7/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr"/>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>沪A08953A</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr"/>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>06:32</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr"/>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB61" s="2" t="inlineStr">
-        <is>
-          <t>78.5</t>
-        </is>
-      </c>
-      <c r="AC61" s="2" t="inlineStr">
-        <is>
-          <t>5/14</t>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>83.5</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>14/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-20-182路.xlsx
+++ b/data/export/2026-10-20-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC67"/>
+  <dimension ref="A1:AC74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,12 +713,12 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,22 +827,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,17 +946,17 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1189,17 +1189,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1546,17 +1546,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1898,7 +1898,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2022,12 +2022,12 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2255,7 +2255,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2374,17 +2374,17 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2493,22 +2493,22 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -2926,7 +2926,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2965,7 +2965,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3085,12 +3085,12 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
@@ -3160,7 +3160,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3204,17 +3204,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3328,12 +3328,12 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -3398,7 +3398,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3452,7 +3452,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3556,7 +3556,7 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3680,12 +3680,12 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
@@ -3755,7 +3755,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3794,7 +3794,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3913,7 +3913,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4032,17 +4032,17 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4112,7 +4112,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4151,22 +4151,22 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -4231,7 +4231,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
@@ -4285,7 +4285,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -4350,7 +4350,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4394,17 +4394,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -4588,7 +4588,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4627,7 +4627,7 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
@@ -4707,7 +4707,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4751,12 +4751,12 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -4945,7 +4945,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4999,7 +4999,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -5064,7 +5064,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5108,12 +5108,12 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
@@ -5183,7 +5183,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5222,7 +5222,7 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
@@ -5302,7 +5302,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5341,17 +5341,17 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA41" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5460,7 +5460,7 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
@@ -5540,7 +5540,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5579,7 +5579,7 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
@@ -5594,7 +5594,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -5778,7 +5778,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5817,7 +5817,7 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5951,7 +5951,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -6016,7 +6016,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6055,7 +6055,7 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
@@ -6135,7 +6135,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6174,7 +6174,7 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
@@ -6254,7 +6254,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6293,22 +6293,22 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA49" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -6369,7 +6369,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6408,7 +6408,7 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6532,17 +6532,17 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6770,12 +6770,12 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
@@ -6845,7 +6845,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6884,7 +6884,7 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA54" s="2" t="inlineStr">
@@ -6937,24 +6937,24 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>71分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6964,7 +6964,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7013,12 +7013,12 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -7046,32 +7046,36 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M56" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -7079,7 +7083,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7103,17 +7107,17 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z56" s="2" t="inlineStr">
@@ -7123,12 +7127,12 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
@@ -7171,24 +7175,24 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -7198,7 +7202,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7237,22 +7241,22 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA57" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -7280,32 +7284,36 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M58" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
           <t>06:32</t>
@@ -7313,7 +7321,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7337,17 +7345,17 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
@@ -7357,17 +7365,17 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -7395,32 +7403,36 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M59" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -7428,7 +7440,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7452,17 +7464,17 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z59" s="2" t="inlineStr">
@@ -7472,17 +7484,17 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -7510,32 +7522,36 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M60" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -7543,7 +7559,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7567,32 +7583,32 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA60" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
@@ -7625,32 +7641,36 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M61" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -7658,7 +7678,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7682,17 +7702,17 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z61" s="2" t="inlineStr">
@@ -7702,12 +7722,12 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
@@ -7773,7 +7793,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7812,7 +7832,7 @@
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA62" s="2" t="inlineStr">
@@ -7888,7 +7908,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7937,12 +7957,12 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -8003,7 +8023,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8042,7 +8062,7 @@
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA64" s="2" t="inlineStr">
@@ -8057,7 +8077,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -8118,7 +8138,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8162,12 +8182,12 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
@@ -8233,7 +8253,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8287,7 +8307,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -8295,22 +8315,22 @@
       <c r="A67" s="2" t="inlineStr"/>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>沪A08953A</t>
+          <t>沪A32298D</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
-        <is>
-          <t>16:20</t>
-        </is>
-      </c>
-      <c r="E67" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -8343,12 +8363,12 @@
       <c r="M67" s="2" t="inlineStr"/>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>06:32</t>
+          <t>07:02</t>
         </is>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8362,47 +8382,852 @@
       <c r="T67" s="2" t="inlineStr"/>
       <c r="U67" s="2" t="inlineStr">
         <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>74.2</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr"/>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>沪A08953A</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
           <t>16:20</t>
         </is>
       </c>
-      <c r="V67" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr"/>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>06:32</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr"/>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="V68" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W67" s="2" t="inlineStr">
+      <c r="W68" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X67" s="2" t="inlineStr">
+      <c r="X68" s="2" t="inlineStr">
         <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Y67" s="2" t="inlineStr">
+      <c r="Y68" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z67" s="2" t="inlineStr">
+      <c r="Z68" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA67" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB67" s="2" t="inlineStr">
-        <is>
-          <t>83.5</t>
-        </is>
-      </c>
-      <c r="AC67" s="2" t="inlineStr">
-        <is>
-          <t>14/14</t>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>80.7</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>10/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr"/>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr"/>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr"/>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>76.8</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>5/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr"/>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>沪A68397D</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr"/>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr"/>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr">
+        <is>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>80.6</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>9/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr"/>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>沪A67983D</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr"/>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr"/>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>78.6</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>7/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr"/>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>沪A12050A</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>16:48</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr"/>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>07:22</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr"/>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr">
+        <is>
+          <t>16:48</t>
+        </is>
+      </c>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr"/>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr"/>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>06:12</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr"/>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>12/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr"/>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr"/>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr"/>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>80.8</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>11/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-20-182路.xlsx
+++ b/data/export/2026-10-20-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC74"/>
+  <dimension ref="A1:AC82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,17 +708,17 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>74.6</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1070,7 +1070,7 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1184,14 +1184,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
           <t>81.2</t>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1308,17 +1308,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1546,17 +1546,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1660,17 +1660,17 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1779,17 +1779,17 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>83.6</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1898,7 +1898,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2017,17 +2017,17 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>74.6</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2136,17 +2136,17 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2508,7 +2508,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
@@ -2692,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2731,14 +2731,14 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
           <t>81.2</t>
@@ -2746,7 +2746,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -2807,7 +2807,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2926,7 +2926,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2970,17 +2970,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -3041,7 +3041,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3080,7 +3080,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
@@ -3160,7 +3160,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3204,17 +3204,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3318,17 +3318,17 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA24" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>83.6</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3437,17 +3437,17 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
@@ -3517,7 +3517,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3556,7 +3556,7 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3675,17 +3675,17 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA27" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>74.6</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
@@ -3755,7 +3755,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3794,17 +3794,17 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA28" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4112,7 +4112,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -4231,7 +4231,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4275,7 +4275,7 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
@@ -4350,7 +4350,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4389,14 +4389,14 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA33" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
           <t>81.2</t>
@@ -4404,7 +4404,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -4469,7 +4469,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4508,7 +4508,7 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
@@ -4588,7 +4588,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4632,17 +4632,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -4707,7 +4707,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4746,7 +4746,7 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4865,17 +4865,17 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA37" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>83.6</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
@@ -4945,7 +4945,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4984,17 +4984,17 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA38" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
@@ -5064,7 +5064,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5103,17 +5103,17 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA39" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>74.6</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
@@ -5183,7 +5183,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5222,17 +5222,17 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA40" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
@@ -5302,7 +5302,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5540,7 +5540,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5584,7 +5584,7 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
@@ -5659,7 +5659,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5698,7 +5698,7 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
@@ -5778,7 +5778,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5822,17 +5822,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -5897,7 +5897,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5936,17 +5936,17 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA46" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
@@ -6016,7 +6016,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6055,7 +6055,7 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
@@ -6135,7 +6135,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6174,17 +6174,17 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA48" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
@@ -6254,7 +6254,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6308,7 +6308,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -6369,7 +6369,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6527,14 +6527,14 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA51" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
           <t>81.2</t>
@@ -6542,7 +6542,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -6607,7 +6607,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6646,7 +6646,7 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
@@ -6726,7 +6726,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6765,7 +6765,7 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA53" s="2" t="inlineStr">
@@ -6845,7 +6845,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6884,7 +6884,7 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA54" s="2" t="inlineStr">
@@ -6964,7 +6964,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7003,17 +7003,17 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA55" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>83.6</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7122,17 +7122,17 @@
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA56" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>74.6</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -7321,7 +7321,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7365,17 +7365,17 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -7440,7 +7440,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7479,14 +7479,14 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA59" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
           <t>81.2</t>
@@ -7494,7 +7494,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7559,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7663,12 +7663,12 @@
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -7678,7 +7678,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7717,7 +7717,7 @@
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA61" s="2" t="inlineStr">
@@ -7760,32 +7760,36 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M62" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
           <t>06:12</t>
@@ -7793,7 +7797,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7817,17 +7821,17 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z62" s="2" t="inlineStr">
@@ -7837,17 +7841,17 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -7875,32 +7879,36 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M63" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -7908,7 +7916,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7932,32 +7940,32 @@
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y63" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA63" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>83.6</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
@@ -7990,32 +7998,36 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M64" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -8023,7 +8035,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8047,17 +8059,17 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z64" s="2" t="inlineStr">
@@ -8067,7 +8079,7 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
@@ -8105,32 +8117,36 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M65" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -8138,7 +8154,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8162,32 +8178,32 @@
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA65" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>74.6</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
@@ -8220,32 +8236,36 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M66" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
           <t>06:42</t>
@@ -8253,7 +8273,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8277,32 +8297,32 @@
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y66" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA66" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
@@ -8335,32 +8355,36 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M67" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
           <t>07:02</t>
@@ -8368,7 +8392,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8392,32 +8416,32 @@
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y67" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA67" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
@@ -8450,32 +8474,36 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M68" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
           <t>06:32</t>
@@ -8483,7 +8511,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8507,17 +8535,17 @@
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y68" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z68" s="2" t="inlineStr">
@@ -8527,17 +8555,17 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -8598,7 +8626,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8637,7 +8665,7 @@
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA69" s="2" t="inlineStr">
@@ -8713,7 +8741,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8767,7 +8795,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -8828,7 +8856,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8943,7 +8971,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9058,7 +9086,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9102,17 +9130,17 @@
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -9120,22 +9148,22 @@
       <c r="A74" s="2" t="inlineStr"/>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>沪A67026D</t>
+          <t>沪A68870D</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
-        <is>
-          <t>17:15</t>
-        </is>
-      </c>
-      <c r="E74" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -9173,7 +9201,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9187,47 +9215,967 @@
       <c r="T74" s="2" t="inlineStr"/>
       <c r="U74" s="2" t="inlineStr">
         <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>81.2</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>12/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr"/>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>沪A02126A</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
           <t>17:15</t>
         </is>
       </c>
-      <c r="V74" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr"/>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>07:52</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr"/>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="V75" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W74" s="2" t="inlineStr">
+      <c r="W75" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X74" s="2" t="inlineStr">
+      <c r="X75" s="2" t="inlineStr">
         <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Y74" s="2" t="inlineStr">
+      <c r="Y75" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z74" s="2" t="inlineStr">
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>68.3</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr"/>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr"/>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr"/>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA74" s="2" t="inlineStr">
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>80.8</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>11/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr"/>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr"/>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr"/>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB74" s="2" t="inlineStr">
-        <is>
-          <t>80.8</t>
-        </is>
-      </c>
-      <c r="AC74" s="2" t="inlineStr">
-        <is>
-          <t>11/14</t>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr"/>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr"/>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr"/>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr"/>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr"/>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>07:02</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr"/>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>74.8</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr"/>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr"/>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr"/>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>83.6</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>14/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr"/>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>18:01</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr"/>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr"/>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr">
+        <is>
+          <t>18:01</t>
+        </is>
+      </c>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>76.8</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>5/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr"/>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr"/>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr"/>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>75.3</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-20-182路.xlsx
+++ b/data/export/2026-10-20-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC82"/>
+  <dimension ref="A1:AC89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,22 +827,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,22 +946,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1184,17 +1184,17 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,22 +1303,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1903,17 +1903,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2255,12 +2255,12 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2374,22 +2374,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2493,22 +2493,22 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2731,17 +2731,17 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
@@ -2807,7 +2807,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2846,17 +2846,17 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>68.3</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2926,7 +2926,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2965,22 +2965,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -3041,7 +3041,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3209,12 +3209,12 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3437,7 +3437,7 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
@@ -3452,7 +3452,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3561,17 +3561,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3755,7 +3755,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3913,12 +3913,12 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4032,22 +4032,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -4112,7 +4112,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4151,22 +4151,22 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -4231,7 +4231,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4285,7 +4285,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -4350,7 +4350,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4389,17 +4389,17 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA33" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -4469,7 +4469,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4508,17 +4508,17 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>68.3</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4588,7 +4588,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4627,22 +4627,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -4707,7 +4707,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4945,7 +4945,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4984,7 +4984,7 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
@@ -4999,7 +4999,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -5064,7 +5064,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5183,7 +5183,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5302,7 +5302,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5341,22 +5341,22 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA41" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -5421,7 +5421,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
@@ -5540,7 +5540,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5594,7 +5594,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -5659,7 +5659,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5698,17 +5698,17 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>68.3</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5778,7 +5778,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5817,22 +5817,22 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA45" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -5897,7 +5897,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5936,7 +5936,7 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
@@ -5951,7 +5951,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -6016,7 +6016,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6060,17 +6060,17 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -6135,7 +6135,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6254,7 +6254,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6293,22 +6293,22 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA49" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -6369,7 +6369,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6408,12 +6408,12 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6527,17 +6527,17 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA51" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
@@ -6607,7 +6607,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6646,17 +6646,17 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>68.3</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6726,7 +6726,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6780,7 +6780,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -6845,7 +6845,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6889,17 +6889,17 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -6964,7 +6964,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7241,22 +7241,22 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA57" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -7321,7 +7321,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7370,12 +7370,12 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -7440,7 +7440,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7479,17 +7479,17 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA59" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
@@ -7559,7 +7559,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7598,22 +7598,22 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA60" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -7678,7 +7678,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7732,7 +7732,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -7797,7 +7797,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7836,22 +7836,22 @@
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA62" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -7916,7 +7916,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -8035,7 +8035,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8089,7 +8089,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8273,7 +8273,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8312,7 +8312,7 @@
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA66" s="2" t="inlineStr">
@@ -8327,7 +8327,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -8392,7 +8392,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
@@ -8511,7 +8511,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8560,12 +8560,12 @@
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -8593,32 +8593,36 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M69" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -8626,7 +8630,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8650,17 +8654,17 @@
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y69" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z69" s="2" t="inlineStr">
@@ -8670,17 +8674,17 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -8708,32 +8712,36 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M70" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -8741,7 +8749,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8765,37 +8773,37 @@
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA70" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -8823,32 +8831,36 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>94分钟</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M71" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -8856,7 +8868,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8880,37 +8892,37 @@
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y71" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA71" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -8938,32 +8950,36 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M72" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
           <t>07:22</t>
@@ -8971,7 +8987,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8995,27 +9011,27 @@
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
@@ -9053,32 +9069,36 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>94分钟</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M73" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
           <t>06:12</t>
@@ -9086,7 +9106,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9110,37 +9130,37 @@
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y73" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA73" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -9168,32 +9188,36 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M74" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -9201,7 +9225,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9225,32 +9249,32 @@
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA74" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
@@ -9283,32 +9307,36 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:36</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M75" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
           <t>07:52</t>
@@ -9316,7 +9344,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9340,32 +9368,32 @@
       </c>
       <c r="W75" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y75" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z75" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>68.3</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
@@ -9431,7 +9459,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9485,7 +9513,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -9546,7 +9574,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9600,7 +9628,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9689,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9700,7 +9728,7 @@
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA78" s="2" t="inlineStr">
@@ -9715,7 +9743,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -9776,7 +9804,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9891,7 +9919,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -10006,7 +10034,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10050,17 +10078,17 @@
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -10121,7 +10149,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10179,6 +10207,811 @@
         </is>
       </c>
     </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr"/>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>沪A68397D</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr"/>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr"/>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>80.8</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>9/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr"/>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>沪A12050A</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>18:31</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr"/>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>07:22</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr"/>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr">
+        <is>
+          <t>18:31</t>
+        </is>
+      </c>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr"/>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>沪A67983D</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr"/>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr"/>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>81.2</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr">
+        <is>
+          <t>10/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr"/>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr"/>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr"/>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>82.3</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr">
+        <is>
+          <t>12/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr"/>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>沪A02126A</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr"/>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr"/>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>07:52</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr"/>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>71.5</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr"/>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr"/>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>06:12</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr"/>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>82.7</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr">
+        <is>
+          <t>13/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr"/>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr"/>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr"/>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>7/14</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-20-182路.xlsx
+++ b/data/export/2026-10-20-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC89"/>
+  <dimension ref="A1:AC94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1070,17 +1070,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1779,17 +1779,17 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>83.6</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2389,7 +2389,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2508,7 +2508,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2617,17 +2617,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2807,7 +2807,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2926,7 +2926,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3080,7 +3080,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
@@ -3214,7 +3214,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3318,17 +3318,17 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA24" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>83.6</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3517,7 +3517,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3561,12 +3561,12 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3755,7 +3755,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3794,7 +3794,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4032,7 +4032,7 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
@@ -4047,7 +4047,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -4112,7 +4112,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -4231,7 +4231,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4275,17 +4275,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -4350,7 +4350,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4469,7 +4469,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4588,7 +4588,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4707,7 +4707,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4746,7 +4746,7 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4865,17 +4865,17 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA37" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>83.6</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
@@ -4945,7 +4945,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5064,7 +5064,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -5183,7 +5183,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5222,7 +5222,7 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
@@ -5302,7 +5302,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5341,7 +5341,7 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
@@ -5356,7 +5356,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -5421,7 +5421,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5540,7 +5540,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5584,17 +5584,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -5659,7 +5659,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5778,7 +5778,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -6016,7 +6016,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6060,12 +6060,12 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
@@ -6135,7 +6135,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6174,7 +6174,7 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
@@ -6254,7 +6254,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6308,7 +6308,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -6369,7 +6369,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6607,7 +6607,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6726,7 +6726,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6765,7 +6765,7 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA53" s="2" t="inlineStr">
@@ -6845,7 +6845,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
@@ -6964,7 +6964,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7003,17 +7003,17 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA55" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>83.6</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7122,7 +7122,7 @@
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -7375,7 +7375,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -7440,7 +7440,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7559,7 +7559,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7598,7 +7598,7 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
@@ -7613,7 +7613,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -7678,7 +7678,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7717,7 +7717,7 @@
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA61" s="2" t="inlineStr">
@@ -7797,7 +7797,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7916,7 +7916,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7955,17 +7955,17 @@
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA63" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>83.6</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
@@ -8035,7 +8035,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8079,17 +8079,17 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8193,7 +8193,7 @@
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA65" s="2" t="inlineStr">
@@ -8273,7 +8273,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8392,7 +8392,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8431,7 +8431,7 @@
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA67" s="2" t="inlineStr">
@@ -8565,7 +8565,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -8630,7 +8630,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8674,12 +8674,12 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
@@ -8749,7 +8749,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8803,7 +8803,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -8868,7 +8868,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8907,7 +8907,7 @@
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA71" s="2" t="inlineStr">
@@ -8922,7 +8922,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -8987,7 +8987,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9106,7 +9106,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9225,7 +9225,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9344,7 +9344,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9426,32 +9426,36 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M76" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -9459,7 +9463,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9483,17 +9487,17 @@
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z76" s="2" t="inlineStr">
@@ -9503,17 +9507,17 @@
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -9574,7 +9578,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9613,7 +9617,7 @@
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA77" s="2" t="inlineStr">
@@ -9689,7 +9693,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9804,7 +9808,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9843,7 +9847,7 @@
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA79" s="2" t="inlineStr">
@@ -9886,32 +9890,36 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M80" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -9919,7 +9927,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9943,32 +9951,32 @@
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z80" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA80" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>83.6</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
@@ -10001,32 +10009,36 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:23</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M81" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -10034,7 +10046,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10058,17 +10070,17 @@
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y81" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z81" s="2" t="inlineStr">
@@ -10078,12 +10090,12 @@
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
@@ -10149,7 +10161,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10188,7 +10200,7 @@
       </c>
       <c r="Z82" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA82" s="2" t="inlineStr">
@@ -10264,7 +10276,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10318,7 +10330,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -10379,7 +10391,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10494,7 +10506,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10533,7 +10545,7 @@
       </c>
       <c r="Z85" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA85" s="2" t="inlineStr">
@@ -10548,7 +10560,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -10609,7 +10621,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10724,7 +10736,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10839,7 +10851,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10901,22 +10913,22 @@
       <c r="A89" s="2" t="inlineStr"/>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>沪A67353D</t>
+          <t>沪A66513D</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
           <t>川沙客运站</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
-        <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="E89" s="2" t="inlineStr">
-        <is>
-          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
@@ -10949,12 +10961,12 @@
       <c r="M89" s="2" t="inlineStr"/>
       <c r="N89" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -10968,47 +10980,622 @@
       <c r="T89" s="2" t="inlineStr"/>
       <c r="U89" s="2" t="inlineStr">
         <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>5/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr"/>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
           <t>19:30</t>
         </is>
       </c>
-      <c r="V89" s="2" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr"/>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr"/>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>19:22</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr"/>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V90" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W89" s="2" t="inlineStr">
+      <c r="W90" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X89" s="2" t="inlineStr">
+      <c r="X90" s="2" t="inlineStr">
         <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Y89" s="2" t="inlineStr">
+      <c r="Y90" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z89" s="2" t="inlineStr">
+      <c r="Z90" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA89" s="2" t="inlineStr">
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>83.8</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr">
+        <is>
+          <t>14/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr"/>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr"/>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr"/>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>19:22</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr"/>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AB89" s="2" t="inlineStr">
+      <c r="AB91" s="2" t="inlineStr">
         <is>
           <t>79.0</t>
         </is>
       </c>
-      <c r="AC89" s="2" t="inlineStr">
+      <c r="AC91" s="2" t="inlineStr">
         <is>
           <t>7/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr"/>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>19:50</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr"/>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr"/>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>19:22</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr"/>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr">
+        <is>
+          <t>19:50</t>
+        </is>
+      </c>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>75.3</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr"/>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>19:55</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr"/>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr"/>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>07:02</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>19:22</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr"/>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr">
+        <is>
+          <t>19:55</t>
+        </is>
+      </c>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>74.8</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr"/>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>沪A67983D</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr"/>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr"/>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>19:22</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr"/>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>81.2</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>9/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-20-182路.xlsx
+++ b/data/export/2026-10-20-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC94"/>
+  <dimension ref="A1:AC97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,17 +832,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>81.9</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,22 +1303,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1660,22 +1660,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2379,17 +2379,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2498,17 +2498,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>81.9</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -2627,7 +2627,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -2807,7 +2807,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2851,12 +2851,12 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2926,7 +2926,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2965,22 +2965,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -3041,7 +3041,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3085,12 +3085,12 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
@@ -3279,7 +3279,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3437,22 +3437,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -3571,7 +3571,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3755,7 +3755,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3794,7 +3794,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3918,12 +3918,12 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4037,17 +4037,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -4112,7 +4112,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4156,17 +4156,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>81.9</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -4285,7 +4285,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -4350,7 +4350,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4404,7 +4404,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -4469,7 +4469,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4588,7 +4588,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4627,22 +4627,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -4707,7 +4707,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4751,12 +4751,12 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4945,7 +4945,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4984,22 +4984,22 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -5064,7 +5064,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5183,7 +5183,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5222,7 +5222,7 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
@@ -5302,7 +5302,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5346,17 +5346,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -5421,7 +5421,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
@@ -5594,7 +5594,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -5659,7 +5659,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5703,12 +5703,12 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5778,7 +5778,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5817,22 +5817,22 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA45" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -5897,7 +5897,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5936,22 +5936,22 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -6070,7 +6070,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -6135,7 +6135,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6174,7 +6174,7 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
@@ -6254,7 +6254,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6298,17 +6298,17 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>81.9</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -6369,7 +6369,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6413,12 +6413,12 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6542,7 +6542,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -6607,7 +6607,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6651,12 +6651,12 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6726,7 +6726,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6770,12 +6770,12 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
@@ -6899,7 +6899,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -6964,7 +6964,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7246,17 +7246,17 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>81.9</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -7440,7 +7440,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7494,7 +7494,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7559,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7603,17 +7603,17 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -7678,7 +7678,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7722,12 +7722,12 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
@@ -7797,7 +7797,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7836,22 +7836,22 @@
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA62" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -7916,7 +7916,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -8089,7 +8089,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8273,7 +8273,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8312,22 +8312,22 @@
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -8392,7 +8392,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8431,7 +8431,7 @@
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA67" s="2" t="inlineStr">
@@ -8684,7 +8684,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -8749,7 +8749,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8793,17 +8793,17 @@
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>81.9</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -8868,7 +8868,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8912,17 +8912,17 @@
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -8987,7 +8987,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
@@ -9106,7 +9106,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9145,22 +9145,22 @@
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA73" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -9225,7 +9225,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9279,7 +9279,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -9344,7 +9344,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9388,12 +9388,12 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
@@ -9517,7 +9517,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -9578,7 +9578,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9622,12 +9622,12 @@
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
@@ -9693,7 +9693,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9732,22 +9732,22 @@
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -9808,7 +9808,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9847,7 +9847,7 @@
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA79" s="2" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -10100,7 +10100,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -10161,7 +10161,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10243,32 +10243,36 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:43</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M83" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -10276,7 +10280,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10300,17 +10304,17 @@
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y83" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z83" s="2" t="inlineStr">
@@ -10320,17 +10324,17 @@
       </c>
       <c r="AA83" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>81.9</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -10358,32 +10362,36 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:46</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M84" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
           <t>07:22</t>
@@ -10391,7 +10399,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10415,17 +10423,17 @@
       </c>
       <c r="W84" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y84" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z84" s="2" t="inlineStr">
@@ -10435,12 +10443,12 @@
       </c>
       <c r="AA84" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
@@ -10473,32 +10481,36 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:58</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M85" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -10506,7 +10518,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10530,17 +10542,17 @@
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y85" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z85" s="2" t="inlineStr">
@@ -10550,17 +10562,17 @@
       </c>
       <c r="AA85" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -10621,7 +10633,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10675,7 +10687,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -10703,32 +10715,36 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M87" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
           <t>07:52</t>
@@ -10736,7 +10752,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10760,17 +10776,17 @@
       </c>
       <c r="W87" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y87" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z87" s="2" t="inlineStr">
@@ -10780,12 +10796,12 @@
       </c>
       <c r="AA87" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
@@ -10818,32 +10834,36 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M88" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
           <t>06:12</t>
@@ -10851,7 +10871,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10875,37 +10895,37 @@
       </c>
       <c r="W88" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y88" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z88" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA88" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -10933,32 +10953,36 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:33</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr"/>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M89" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -10966,7 +10990,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -10990,17 +11014,17 @@
       </c>
       <c r="W89" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y89" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z89" s="2" t="inlineStr">
@@ -11010,12 +11034,12 @@
       </c>
       <c r="AA89" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
@@ -11081,7 +11105,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11163,32 +11187,36 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr"/>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M91" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
           <t>06:42</t>
@@ -11196,7 +11224,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11220,37 +11248,37 @@
       </c>
       <c r="W91" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y91" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z91" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA91" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -11311,7 +11339,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11426,7 +11454,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11465,7 +11493,7 @@
       </c>
       <c r="Z93" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA93" s="2" t="inlineStr">
@@ -11541,7 +11569,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11585,17 +11613,362 @@
       </c>
       <c r="AA94" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>80.7</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr"/>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr"/>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr"/>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>06:12</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>20:22</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr"/>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>81.3</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>9/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr"/>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>20:50</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr"/>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr"/>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>20:22</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr"/>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr">
+        <is>
+          <t>20:50</t>
+        </is>
+      </c>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W96" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z96" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA96" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AB94" s="2" t="inlineStr">
-        <is>
-          <t>81.2</t>
-        </is>
-      </c>
-      <c r="AC94" s="2" t="inlineStr">
-        <is>
-          <t>9/14</t>
+      <c r="AB96" s="2" t="inlineStr">
+        <is>
+          <t>77.8</t>
+        </is>
+      </c>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr"/>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>21:15</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr"/>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr"/>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>07:02</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>20:22</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr"/>
+      <c r="R97" s="2" t="inlineStr"/>
+      <c r="S97" s="2" t="inlineStr"/>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr">
+        <is>
+          <t>21:15</t>
+        </is>
+      </c>
+      <c r="V97" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z97" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA97" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr">
+        <is>
+          <t>74.8</t>
+        </is>
+      </c>
+      <c r="AC97" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-20-182路.xlsx
+++ b/data/export/2026-10-20-182路.xlsx
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,12 +713,12 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -951,12 +951,12 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1670,7 +1670,7 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1784,17 +1784,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2022,12 +2022,12 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2141,12 +2141,12 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2379,12 +2379,12 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -2926,7 +2926,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2970,12 +2970,12 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3279,7 +3279,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3323,17 +3323,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -3398,7 +3398,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3680,12 +3680,12 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
@@ -3755,7 +3755,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3799,12 +3799,12 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4037,12 +4037,12 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4404,7 +4404,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -4588,7 +4588,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4632,12 +4632,12 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4870,17 +4870,17 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -4945,7 +4945,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4994,7 +4994,7 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
@@ -5064,7 +5064,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5108,12 +5108,12 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
@@ -5183,7 +5183,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5227,12 +5227,12 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
@@ -5302,7 +5302,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5346,12 +5346,12 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5778,7 +5778,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5946,7 +5946,7 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
@@ -6135,7 +6135,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6179,12 +6179,12 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
@@ -6542,7 +6542,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -6964,7 +6964,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7008,17 +7008,17 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7127,12 +7127,12 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
@@ -7494,7 +7494,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7559,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7603,12 +7603,12 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
@@ -7797,7 +7797,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7841,12 +7841,12 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
@@ -7916,7 +7916,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7960,17 +7960,17 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8198,12 +8198,12 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
@@ -8273,7 +8273,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8322,7 +8322,7 @@
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
@@ -8392,7 +8392,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8436,12 +8436,12 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
@@ -8868,7 +8868,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
@@ -9106,7 +9106,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9150,12 +9150,12 @@
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
@@ -9279,7 +9279,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -9693,7 +9693,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9742,7 +9742,7 @@
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
@@ -9808,7 +9808,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9852,12 +9852,12 @@
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9971,17 +9971,17 @@
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -10161,7 +10161,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10205,12 +10205,12 @@
       </c>
       <c r="AA82" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
@@ -10518,7 +10518,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10562,12 +10562,12 @@
       </c>
       <c r="AA85" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
@@ -10687,7 +10687,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -10871,7 +10871,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10915,12 +10915,12 @@
       </c>
       <c r="AA88" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
@@ -11072,32 +11072,36 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:43</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M90" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -11105,7 +11109,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11129,17 +11133,17 @@
       </c>
       <c r="W90" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y90" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z90" s="2" t="inlineStr">
@@ -11149,17 +11153,17 @@
       </c>
       <c r="AA90" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -11197,24 +11201,24 @@
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>20:42</t>
+          <t>20:43</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr"/>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
@@ -11224,7 +11228,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11273,7 +11277,7 @@
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
@@ -11306,32 +11310,36 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:03</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M92" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -11339,7 +11347,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11363,17 +11371,17 @@
       </c>
       <c r="W92" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y92" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z92" s="2" t="inlineStr">
@@ -11383,12 +11391,12 @@
       </c>
       <c r="AA92" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
@@ -11421,32 +11429,36 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:05</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr"/>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M93" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
           <t>07:02</t>
@@ -11454,7 +11466,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11478,17 +11490,17 @@
       </c>
       <c r="W93" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y93" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z93" s="2" t="inlineStr">
@@ -11498,12 +11510,12 @@
       </c>
       <c r="AA93" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
@@ -11536,32 +11548,36 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:27</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M94" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -11569,7 +11585,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11593,17 +11609,17 @@
       </c>
       <c r="W94" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y94" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z94" s="2" t="inlineStr">
@@ -11613,12 +11629,12 @@
       </c>
       <c r="AA94" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
@@ -11651,32 +11667,36 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr"/>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M95" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
           <t>06:12</t>
@@ -11684,7 +11704,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11708,17 +11728,17 @@
       </c>
       <c r="W95" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y95" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z95" s="2" t="inlineStr">
@@ -11728,12 +11748,12 @@
       </c>
       <c r="AA95" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB95" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="AC95" s="2" t="inlineStr">
@@ -11799,7 +11819,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11848,7 +11868,7 @@
       </c>
       <c r="AB96" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC96" s="2" t="inlineStr">
@@ -11914,7 +11934,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11958,12 +11978,12 @@
       </c>
       <c r="AA97" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
